--- a/apps/excel-service/templates/NomadDocs/Tax Invoice.xlsx
+++ b/apps/excel-service/templates/NomadDocs/Tax Invoice.xlsx
@@ -158,7 +158,7 @@
         <color theme="1"/>
         <rFont val="Arial"/>
       </rPr>
-      <t xml:space="preserve">БИН: {organization.bin}, {organization.address}</t>
+      <t xml:space="preserve">БИН: {organization.bin}, город {organization.city}, {organization.index}, {organization.address}</t>
     </r>
   </si>
   <si>
@@ -271,7 +271,6 @@
   <fonts count="8">
     <font>
       <sz val="8.000000"/>
-      <color indexed="64"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
@@ -338,20 +337,20 @@
       <right style="none"/>
       <top style="none"/>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="medium">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="none"/>
       <top style="medium">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
@@ -359,36 +358,36 @@
       <left style="none"/>
       <right style="none"/>
       <top style="medium">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="none"/>
       <right style="medium">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="medium">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="medium">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="none"/>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
@@ -396,81 +395,81 @@
       <left style="none"/>
       <right style="none"/>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="none"/>
       <right style="medium">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="none"/>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="none"/>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="medium">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="none"/>
       <top style="none"/>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="none"/>
       <right style="medium">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="none"/>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="medium">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="none"/>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="none"/>
       <diagonal style="none"/>
@@ -479,7 +478,7 @@
       <left style="none"/>
       <right style="none"/>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="none"/>
       <diagonal style="none"/>
@@ -487,143 +486,143 @@
     <border>
       <left style="none"/>
       <right style="medium">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="none"/>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="medium">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="none"/>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="none"/>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="none"/>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="none"/>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="medium">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="none"/>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="none"/>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="none"/>
       <top style="none"/>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="medium">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="medium">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="medium">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="none"/>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="medium">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
@@ -631,66 +630,66 @@
       <left style="none"/>
       <right style="none"/>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="medium">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="none"/>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="medium">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="none"/>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="medium">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="medium">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </left>
       <right style="medium">
-        <color indexed="64"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color auto="1"/>
       </top>
       <bottom style="medium">
-        <color indexed="64"/>
+        <color auto="1"/>
       </bottom>
       <diagonal style="none"/>
     </border>

--- a/apps/excel-service/templates/NomadDocs/Tax Invoice.xlsx
+++ b/apps/excel-service/templates/NomadDocs/Tax Invoice.xlsx
@@ -178,7 +178,7 @@
         <color theme="1"/>
         <rFont val="Arial"/>
       </rPr>
-      <t xml:space="preserve"> {organization.iik}, {organization.bank}, БИК {organization.bik}, КБЕ {organization.kbe} {organization.knp}</t>
+      <t xml:space="preserve"> {organization.iik}, {organization.bank}, БИК {organization.bik}, {organization.kbe} {organization.knp}</t>
     </r>
   </si>
   <si>

--- a/apps/excel-service/templates/NomadDocs/Tax Invoice.xlsx
+++ b/apps/excel-service/templates/NomadDocs/Tax Invoice.xlsx
@@ -224,23 +224,23 @@
     <t>{nights}</t>
   </si>
   <si>
-    <t>{organization.costPerDay}</t>
+    <t>{costPerDayFormatted}</t>
   </si>
   <si>
-    <t>{totalPrice}</t>
+    <t>{totalCost}</t>
   </si>
   <si>
     <t xml:space="preserve">без НДС</t>
   </si>
   <si>
     <t xml:space="preserve">
-{totalPrice}</t>
+{totalCost}</t>
   </si>
   <si>
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t xml:space="preserve">Всего по счету:  {totalPriceWords} тенге 00 тиын</t>
+    <t xml:space="preserve">Всего по счету:  {totalCostRu} тенге 00 тиын</t>
   </si>
   <si>
     <t xml:space="preserve">Руководитель: Жалтырбаев Ә.Ғ.</t>

--- a/apps/excel-service/templates/NomadDocs/Tax Invoice.xlsx
+++ b/apps/excel-service/templates/NomadDocs/Tax Invoice.xlsx
@@ -138,7 +138,7 @@
         <color theme="1"/>
         <rFont val="Arial"/>
       </rPr>
-      <t>{organization.organization}</t>
+      <t>{customer.organization.organization}</t>
     </r>
   </si>
   <si>
@@ -158,7 +158,7 @@
         <color theme="1"/>
         <rFont val="Arial"/>
       </rPr>
-      <t xml:space="preserve">БИН: {organization.bin}, город {organization.city}, {organization.index}, {organization.address}</t>
+      <t xml:space="preserve">БИН: {customer.organization.bin}, город {customer.organization.city}, {customer.organization.index}, {customer.organization.address}</t>
     </r>
   </si>
   <si>
@@ -178,7 +178,7 @@
         <color theme="1"/>
         <rFont val="Arial"/>
       </rPr>
-      <t xml:space="preserve"> {organization.iik}, {organization.bank}, БИК {organization.bik}, {organization.kbe} {organization.knp}</t>
+      <t xml:space="preserve"> {customer.organization.iik}, {customer.organization.bank}, БИК {customer.organization.bik}, {customer.organization.kbe} {organization.knp}</t>
     </r>
   </si>
   <si>

--- a/apps/excel-service/templates/NomadDocs/Tax Invoice.xlsx
+++ b/apps/excel-service/templates/NomadDocs/Tax Invoice.xlsx
@@ -158,7 +158,7 @@
         <color theme="1"/>
         <rFont val="Arial"/>
       </rPr>
-      <t xml:space="preserve">БИН: {customer.organization.bin}, город {customer.organization.city}, {customer.organization.index}, {customer.organization.address}</t>
+      <t xml:space="preserve">БИН: {customer.organization.bin}, город {customer.organization.city}, {customer.organization.index} {customer.organization.address}</t>
     </r>
   </si>
   <si>

--- a/apps/excel-service/templates/NomadDocs/Tax Invoice.xlsx
+++ b/apps/excel-service/templates/NomadDocs/Tax Invoice.xlsx
@@ -178,7 +178,7 @@
         <color theme="1"/>
         <rFont val="Arial"/>
       </rPr>
-      <t xml:space="preserve"> {customer.organization.iik}, {customer.organization.bank}, БИК {customer.organization.bik}, {customer.organization.kbe} {organization.knp}</t>
+      <t xml:space="preserve"> {customer.organization.iik}, {customer.organization.bank}, БИК {customer.organization.bik}, {customer.organization.kbe} {customer.organization.knp}</t>
     </r>
   </si>
   <si>

--- a/apps/excel-service/templates/NomadDocs/Tax Invoice.xlsx
+++ b/apps/excel-service/templates/NomadDocs/Tax Invoice.xlsx
@@ -240,7 +240,7 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t xml:space="preserve">Всего по счету:  {totalCostRu} тенге 00 тиын</t>
+    <t xml:space="preserve">Всего по счету:  {totalCostRu} тенге{totalCostCentsRu} тиын</t>
   </si>
   <si>
     <t xml:space="preserve">Руководитель: Жалтырбаев Ә.Ғ.</t>
